--- a/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-organization.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T12:31:41+00:00</t>
+    <t>2026-01-28T09:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -718,7 +718,7 @@
     <t>Organization.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
